--- a/RSSH-profile-dash/data/world-bank-income-groups.xlsx
+++ b/RSSH-profile-dash/data/world-bank-income-groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommeijer/Git/RSSH-profile-dash/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBC9FA33-2238-0F4B-9723-BE970D8CA97F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB13F15-87CA-9143-BCC7-EC6A0074EC24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="600" windowWidth="38400" windowHeight="19200" xr2:uid="{7D3FF3BD-7310-6946-96D8-A03C304B4620}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21600" xr2:uid="{7D3FF3BD-7310-6946-96D8-A03C304B4620}"/>
   </bookViews>
   <sheets>
     <sheet name="world-bank-income-groups" sheetId="1" r:id="rId1"/>
@@ -1851,7 +1851,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1">
+    <row r="101" spans="1:3">
       <c r="A101" t="s">
         <v>9</v>
       </c>
@@ -2951,7 +2951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1">
+    <row r="126" spans="1:3">
       <c r="A126" t="s">
         <v>11</v>
       </c>
@@ -3226,7 +3226,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1">
+    <row r="151" spans="1:3">
       <c r="A151" t="s">
         <v>12</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1">
+    <row r="176" spans="1:3">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -4326,7 +4326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1">
+    <row r="251" spans="1:3">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1">
+    <row r="276" spans="1:3">
       <c r="A276" t="s">
         <v>17</v>
       </c>
@@ -4876,7 +4876,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1">
+    <row r="301" spans="1:3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -5426,7 +5426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1">
+    <row r="351" spans="1:3">
       <c r="A351" t="s">
         <v>20</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:3" hidden="1">
+    <row r="376" spans="1:3">
       <c r="A376" t="s">
         <v>21</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="401" spans="1:3" hidden="1">
+    <row r="401" spans="1:3">
       <c r="A401" t="s">
         <v>22</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:3" hidden="1">
+    <row r="426" spans="1:3">
       <c r="A426" t="s">
         <v>23</v>
       </c>
@@ -6801,7 +6801,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:3" hidden="1">
+    <row r="476" spans="1:3">
       <c r="A476" t="s">
         <v>25</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="526" spans="1:3" hidden="1">
+    <row r="526" spans="1:3">
       <c r="A526" t="s">
         <v>27</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="551" spans="1:3" hidden="1">
+    <row r="551" spans="1:3">
       <c r="A551" t="s">
         <v>28</v>
       </c>
@@ -7901,7 +7901,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="576" spans="1:3" hidden="1">
+    <row r="576" spans="1:3">
       <c r="A576" t="s">
         <v>29</v>
       </c>
@@ -8176,7 +8176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="601" spans="1:3" hidden="1">
+    <row r="601" spans="1:3">
       <c r="A601" t="s">
         <v>30</v>
       </c>
@@ -9111,7 +9111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="686" spans="1:3" hidden="1">
+    <row r="686" spans="1:3">
       <c r="A686" t="s">
         <v>34</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="711" spans="1:3" hidden="1">
+    <row r="711" spans="1:3">
       <c r="A711" t="s">
         <v>35</v>
       </c>
@@ -9661,7 +9661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="736" spans="1:3" hidden="1">
+    <row r="736" spans="1:3">
       <c r="A736" t="s">
         <v>36</v>
       </c>
@@ -9936,7 +9936,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="761" spans="1:3" hidden="1">
+    <row r="761" spans="1:3">
       <c r="A761" t="s">
         <v>37</v>
       </c>
@@ -10211,7 +10211,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="786" spans="1:3" hidden="1">
+    <row r="786" spans="1:3">
       <c r="A786" t="s">
         <v>38</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="811" spans="1:3" hidden="1">
+    <row r="811" spans="1:3">
       <c r="A811" t="s">
         <v>39</v>
       </c>
@@ -10761,7 +10761,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="836" spans="1:3" hidden="1">
+    <row r="836" spans="1:3">
       <c r="A836" t="s">
         <v>40</v>
       </c>
@@ -11036,7 +11036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="861" spans="1:3" hidden="1">
+    <row r="861" spans="1:3">
       <c r="A861" t="s">
         <v>41</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="911" spans="1:3" hidden="1">
+    <row r="911" spans="1:3">
       <c r="A911" t="s">
         <v>43</v>
       </c>
@@ -11861,7 +11861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="936" spans="1:3" hidden="1">
+    <row r="936" spans="1:3">
       <c r="A936" t="s">
         <v>44</v>
       </c>
@@ -12136,7 +12136,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="961" spans="1:3" hidden="1">
+    <row r="961" spans="1:3">
       <c r="A961" t="s">
         <v>45</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="986" spans="1:3" hidden="1">
+    <row r="986" spans="1:3">
       <c r="A986" t="s">
         <v>46</v>
       </c>
@@ -12686,7 +12686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1011" spans="1:3" hidden="1">
+    <row r="1011" spans="1:3">
       <c r="A1011" t="s">
         <v>47</v>
       </c>
@@ -13511,7 +13511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1086" spans="1:3" hidden="1">
+    <row r="1086" spans="1:3">
       <c r="A1086" t="s">
         <v>50</v>
       </c>
@@ -13786,7 +13786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1111" spans="1:3" hidden="1">
+    <row r="1111" spans="1:3">
       <c r="A1111" t="s">
         <v>51</v>
       </c>
@@ -14061,7 +14061,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1136" spans="1:3" hidden="1">
+    <row r="1136" spans="1:3">
       <c r="A1136" t="s">
         <v>52</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1161" spans="1:3" hidden="1">
+    <row r="1161" spans="1:3">
       <c r="A1161" t="s">
         <v>53</v>
       </c>
@@ -14611,7 +14611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1186" spans="1:3" hidden="1">
+    <row r="1186" spans="1:3">
       <c r="A1186" t="s">
         <v>54</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1226" spans="1:3" hidden="1">
+    <row r="1226" spans="1:3">
       <c r="A1226" t="s">
         <v>56</v>
       </c>
@@ -15326,7 +15326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1251" spans="1:3" hidden="1">
+    <row r="1251" spans="1:3">
       <c r="A1251" t="s">
         <v>57</v>
       </c>
@@ -15601,7 +15601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1276" spans="1:3" hidden="1">
+    <row r="1276" spans="1:3">
       <c r="A1276" t="s">
         <v>58</v>
       </c>
@@ -15876,7 +15876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1301" spans="1:3" hidden="1">
+    <row r="1301" spans="1:3">
       <c r="A1301" t="s">
         <v>59</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1326" spans="1:3" hidden="1">
+    <row r="1326" spans="1:3">
       <c r="A1326" t="s">
         <v>60</v>
       </c>
@@ -16426,7 +16426,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1351" spans="1:3" hidden="1">
+    <row r="1351" spans="1:3">
       <c r="A1351" t="s">
         <v>61</v>
       </c>
@@ -17240,7 +17240,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1425" spans="1:3" hidden="1">
+    <row r="1425" spans="1:3">
       <c r="A1425" t="s">
         <v>64</v>
       </c>
@@ -17790,7 +17790,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1475" spans="1:3" hidden="1">
+    <row r="1475" spans="1:3">
       <c r="A1475" t="s">
         <v>66</v>
       </c>
@@ -18615,7 +18615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1550" spans="1:3" hidden="1">
+    <row r="1550" spans="1:3">
       <c r="A1550" t="s">
         <v>69</v>
       </c>
@@ -18890,7 +18890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1575" spans="1:3" hidden="1">
+    <row r="1575" spans="1:3">
       <c r="A1575" t="s">
         <v>70</v>
       </c>
@@ -19165,7 +19165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1600" spans="1:3" hidden="1">
+    <row r="1600" spans="1:3">
       <c r="A1600" t="s">
         <v>71</v>
       </c>
@@ -19704,7 +19704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1649" spans="1:3" hidden="1">
+    <row r="1649" spans="1:3">
       <c r="A1649" t="s">
         <v>73</v>
       </c>
@@ -20254,7 +20254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1699" spans="1:3" hidden="1">
+    <row r="1699" spans="1:3">
       <c r="A1699" t="s">
         <v>75</v>
       </c>
@@ -20529,7 +20529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1724" spans="1:3" hidden="1">
+    <row r="1724" spans="1:3">
       <c r="A1724" t="s">
         <v>76</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1749" spans="1:3" hidden="1">
+    <row r="1749" spans="1:3">
       <c r="A1749" t="s">
         <v>77</v>
       </c>
@@ -21079,7 +21079,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1774" spans="1:3" hidden="1">
+    <row r="1774" spans="1:3">
       <c r="A1774" t="s">
         <v>78</v>
       </c>
@@ -21354,7 +21354,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1799" spans="1:3" hidden="1">
+    <row r="1799" spans="1:3">
       <c r="A1799" t="s">
         <v>79</v>
       </c>
@@ -21904,7 +21904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="1849" spans="1:3" hidden="1">
+    <row r="1849" spans="1:3">
       <c r="A1849" t="s">
         <v>81</v>
       </c>
@@ -22454,7 +22454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1899" spans="1:3" hidden="1">
+    <row r="1899" spans="1:3">
       <c r="A1899" t="s">
         <v>83</v>
       </c>
@@ -22729,7 +22729,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="1924" spans="1:3" hidden="1">
+    <row r="1924" spans="1:3">
       <c r="A1924" t="s">
         <v>84</v>
       </c>
@@ -22861,7 +22861,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1936" spans="1:3" hidden="1">
+    <row r="1936" spans="1:3">
       <c r="A1936" t="s">
         <v>85</v>
       </c>
@@ -23136,7 +23136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1961" spans="1:3" hidden="1">
+    <row r="1961" spans="1:3">
       <c r="A1961" t="s">
         <v>86</v>
       </c>
@@ -23411,7 +23411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1986" spans="1:3" hidden="1">
+    <row r="1986" spans="1:3">
       <c r="A1986" t="s">
         <v>87</v>
       </c>
@@ -23961,7 +23961,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2036" spans="1:3" hidden="1">
+    <row r="2036" spans="1:3">
       <c r="A2036" t="s">
         <v>89</v>
       </c>
@@ -24511,7 +24511,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2086" spans="1:3" hidden="1">
+    <row r="2086" spans="1:3">
       <c r="A2086" t="s">
         <v>91</v>
       </c>
@@ -24786,7 +24786,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2111" spans="1:3" hidden="1">
+    <row r="2111" spans="1:3">
       <c r="A2111" t="s">
         <v>92</v>
       </c>
@@ -25061,7 +25061,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2136" spans="1:3" hidden="1">
+    <row r="2136" spans="1:3">
       <c r="A2136" t="s">
         <v>93</v>
       </c>
@@ -25336,7 +25336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2161" spans="1:3" hidden="1">
+    <row r="2161" spans="1:3">
       <c r="A2161" t="s">
         <v>94</v>
       </c>
@@ -25611,7 +25611,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2186" spans="1:3" hidden="1">
+    <row r="2186" spans="1:3">
       <c r="A2186" t="s">
         <v>95</v>
       </c>
@@ -25886,7 +25886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2211" spans="1:3" hidden="1">
+    <row r="2211" spans="1:3">
       <c r="A2211" t="s">
         <v>96</v>
       </c>
@@ -26161,7 +26161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2236" spans="1:3" hidden="1">
+    <row r="2236" spans="1:3">
       <c r="A2236" t="s">
         <v>97</v>
       </c>
@@ -26436,7 +26436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2261" spans="1:3" hidden="1">
+    <row r="2261" spans="1:3">
       <c r="A2261" t="s">
         <v>98</v>
       </c>
@@ -26711,7 +26711,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2286" spans="1:3" hidden="1">
+    <row r="2286" spans="1:3">
       <c r="A2286" t="s">
         <v>99</v>
       </c>
@@ -27811,7 +27811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2386" spans="1:3" hidden="1">
+    <row r="2386" spans="1:3">
       <c r="A2386" t="s">
         <v>103</v>
       </c>
@@ -28086,7 +28086,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2411" spans="1:3" hidden="1">
+    <row r="2411" spans="1:3">
       <c r="A2411" t="s">
         <v>104</v>
       </c>
@@ -28361,7 +28361,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2436" spans="1:3" hidden="1">
+    <row r="2436" spans="1:3">
       <c r="A2436" t="s">
         <v>105</v>
       </c>
@@ -28636,7 +28636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2461" spans="1:3" hidden="1">
+    <row r="2461" spans="1:3">
       <c r="A2461" t="s">
         <v>106</v>
       </c>
@@ -29186,7 +29186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2511" spans="1:3" hidden="1">
+    <row r="2511" spans="1:3">
       <c r="A2511" t="s">
         <v>108</v>
       </c>
@@ -29461,7 +29461,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2536" spans="1:3" hidden="1">
+    <row r="2536" spans="1:3">
       <c r="A2536" t="s">
         <v>109</v>
       </c>
@@ -30011,7 +30011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2586" spans="1:3" hidden="1">
+    <row r="2586" spans="1:3">
       <c r="A2586" t="s">
         <v>111</v>
       </c>
@@ -30286,7 +30286,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2611" spans="1:3" hidden="1">
+    <row r="2611" spans="1:3">
       <c r="A2611" t="s">
         <v>112</v>
       </c>
@@ -30748,7 +30748,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2653" spans="1:3" hidden="1">
+    <row r="2653" spans="1:3">
       <c r="A2653" t="s">
         <v>114</v>
       </c>
@@ -31023,7 +31023,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2678" spans="1:3" hidden="1">
+    <row r="2678" spans="1:3">
       <c r="A2678" t="s">
         <v>115</v>
       </c>
@@ -31298,7 +31298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2703" spans="1:3" hidden="1">
+    <row r="2703" spans="1:3">
       <c r="A2703" t="s">
         <v>116</v>
       </c>
@@ -31573,7 +31573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2728" spans="1:3" hidden="1">
+    <row r="2728" spans="1:3">
       <c r="A2728" t="s">
         <v>117</v>
       </c>
@@ -31848,7 +31848,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2753" spans="1:3" hidden="1">
+    <row r="2753" spans="1:3">
       <c r="A2753" t="s">
         <v>118</v>
       </c>
@@ -32123,7 +32123,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2778" spans="1:3" hidden="1">
+    <row r="2778" spans="1:3">
       <c r="A2778" t="s">
         <v>119</v>
       </c>
@@ -32398,7 +32398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2803" spans="1:3" hidden="1">
+    <row r="2803" spans="1:3">
       <c r="A2803" t="s">
         <v>120</v>
       </c>
@@ -32948,7 +32948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2853" spans="1:3" hidden="1">
+    <row r="2853" spans="1:3">
       <c r="A2853" t="s">
         <v>122</v>
       </c>
@@ -33223,7 +33223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2878" spans="1:3" hidden="1">
+    <row r="2878" spans="1:3">
       <c r="A2878" t="s">
         <v>123</v>
       </c>
@@ -33498,7 +33498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2903" spans="1:3" hidden="1">
+    <row r="2903" spans="1:3">
       <c r="A2903" t="s">
         <v>124</v>
       </c>
@@ -33773,7 +33773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2928" spans="1:3" hidden="1">
+    <row r="2928" spans="1:3">
       <c r="A2928" t="s">
         <v>125</v>
       </c>
@@ -34048,7 +34048,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2953" spans="1:3" hidden="1">
+    <row r="2953" spans="1:3">
       <c r="A2953" t="s">
         <v>126</v>
       </c>
@@ -34323,7 +34323,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2978" spans="1:3" hidden="1">
+    <row r="2978" spans="1:3">
       <c r="A2978" t="s">
         <v>127</v>
       </c>
@@ -35148,7 +35148,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3053" spans="1:3" hidden="1">
+    <row r="3053" spans="1:3">
       <c r="A3053" t="s">
         <v>130</v>
       </c>
@@ -35423,7 +35423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3078" spans="1:3" hidden="1">
+    <row r="3078" spans="1:3">
       <c r="A3078" t="s">
         <v>131</v>
       </c>
@@ -35973,7 +35973,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3128" spans="1:3" hidden="1">
+    <row r="3128" spans="1:3">
       <c r="A3128" t="s">
         <v>133</v>
       </c>
@@ -36919,7 +36919,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3214" spans="1:3" hidden="1">
+    <row r="3214" spans="1:3">
       <c r="A3214" t="s">
         <v>137</v>
       </c>
@@ -37469,7 +37469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3264" spans="1:3" hidden="1">
+    <row r="3264" spans="1:3">
       <c r="A3264" t="s">
         <v>139</v>
       </c>
@@ -38228,7 +38228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3333" spans="1:3" hidden="1">
+    <row r="3333" spans="1:3">
       <c r="A3333" t="s">
         <v>142</v>
       </c>
@@ -38503,7 +38503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3358" spans="1:3" hidden="1">
+    <row r="3358" spans="1:3">
       <c r="A3358" t="s">
         <v>143</v>
       </c>
@@ -38778,7 +38778,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3383" spans="1:3" hidden="1">
+    <row r="3383" spans="1:3">
       <c r="A3383" t="s">
         <v>144</v>
       </c>
@@ -39053,7 +39053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3408" spans="1:3" hidden="1">
+    <row r="3408" spans="1:3">
       <c r="A3408" t="s">
         <v>145</v>
       </c>
@@ -39163,7 +39163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3418" spans="1:3" hidden="1">
+    <row r="3418" spans="1:3">
       <c r="A3418" t="s">
         <v>146</v>
       </c>
@@ -39438,7 +39438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3443" spans="1:3" hidden="1">
+    <row r="3443" spans="1:3">
       <c r="A3443" t="s">
         <v>147</v>
       </c>
@@ -39713,7 +39713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3468" spans="1:3" hidden="1">
+    <row r="3468" spans="1:3">
       <c r="A3468" t="s">
         <v>148</v>
       </c>
@@ -40098,7 +40098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3503" spans="1:3" hidden="1">
+    <row r="3503" spans="1:3">
       <c r="A3503" t="s">
         <v>150</v>
       </c>
@@ -40373,7 +40373,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3528" spans="1:3" hidden="1">
+    <row r="3528" spans="1:3">
       <c r="A3528" t="s">
         <v>151</v>
       </c>
@@ -40648,7 +40648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3553" spans="1:3" hidden="1">
+    <row r="3553" spans="1:3">
       <c r="A3553" t="s">
         <v>152</v>
       </c>
@@ -40923,7 +40923,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3578" spans="1:3" hidden="1">
+    <row r="3578" spans="1:3">
       <c r="A3578" t="s">
         <v>153</v>
       </c>
@@ -41198,7 +41198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3603" spans="1:3" hidden="1">
+    <row r="3603" spans="1:3">
       <c r="A3603" t="s">
         <v>154</v>
       </c>
@@ -41473,7 +41473,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3628" spans="1:3" hidden="1">
+    <row r="3628" spans="1:3">
       <c r="A3628" t="s">
         <v>155</v>
       </c>
@@ -42023,7 +42023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3678" spans="1:3" hidden="1">
+    <row r="3678" spans="1:3">
       <c r="A3678" t="s">
         <v>157</v>
       </c>
@@ -42298,7 +42298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3703" spans="1:3" hidden="1">
+    <row r="3703" spans="1:3">
       <c r="A3703" t="s">
         <v>158</v>
       </c>
@@ -42573,7 +42573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3728" spans="1:3" hidden="1">
+    <row r="3728" spans="1:3">
       <c r="A3728" t="s">
         <v>159</v>
       </c>
@@ -42848,7 +42848,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3753" spans="1:3" hidden="1">
+    <row r="3753" spans="1:3">
       <c r="A3753" t="s">
         <v>160</v>
       </c>
@@ -43123,7 +43123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3778" spans="1:3" hidden="1">
+    <row r="3778" spans="1:3">
       <c r="A3778" t="s">
         <v>161</v>
       </c>
@@ -43398,7 +43398,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3803" spans="1:3" hidden="1">
+    <row r="3803" spans="1:3">
       <c r="A3803" t="s">
         <v>162</v>
       </c>
@@ -43673,7 +43673,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3828" spans="1:3" hidden="1">
+    <row r="3828" spans="1:3">
       <c r="A3828" t="s">
         <v>163</v>
       </c>
@@ -43948,7 +43948,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3853" spans="1:3" hidden="1">
+    <row r="3853" spans="1:3">
       <c r="A3853" t="s">
         <v>164</v>
       </c>
@@ -44773,7 +44773,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3928" spans="1:3" hidden="1">
+    <row r="3928" spans="1:3">
       <c r="A3928" t="s">
         <v>167</v>
       </c>
@@ -45048,7 +45048,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3953" spans="1:3" hidden="1">
+    <row r="3953" spans="1:3">
       <c r="A3953" t="s">
         <v>168</v>
       </c>
@@ -45323,7 +45323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3978" spans="1:3" hidden="1">
+    <row r="3978" spans="1:3">
       <c r="A3978" t="s">
         <v>169</v>
       </c>
@@ -45598,7 +45598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4003" spans="1:3" hidden="1">
+    <row r="4003" spans="1:3">
       <c r="A4003" t="s">
         <v>170</v>
       </c>
@@ -45873,7 +45873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4028" spans="1:3" hidden="1">
+    <row r="4028" spans="1:3">
       <c r="A4028" t="s">
         <v>171</v>
       </c>
@@ -46148,7 +46148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4053" spans="1:3" hidden="1">
+    <row r="4053" spans="1:3">
       <c r="A4053" t="s">
         <v>172</v>
       </c>
@@ -46423,7 +46423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4078" spans="1:3" hidden="1">
+    <row r="4078" spans="1:3">
       <c r="A4078" t="s">
         <v>173</v>
       </c>
@@ -46698,7 +46698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4103" spans="1:3" hidden="1">
+    <row r="4103" spans="1:3">
       <c r="A4103" t="s">
         <v>174</v>
       </c>
@@ -46973,7 +46973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4128" spans="1:3" hidden="1">
+    <row r="4128" spans="1:3">
       <c r="A4128" t="s">
         <v>175</v>
       </c>
@@ -47413,7 +47413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4168" spans="1:3" hidden="1">
+    <row r="4168" spans="1:3">
       <c r="A4168" t="s">
         <v>177</v>
       </c>
@@ -48238,7 +48238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4243" spans="1:3" hidden="1">
+    <row r="4243" spans="1:3">
       <c r="A4243" t="s">
         <v>180</v>
       </c>
@@ -48513,7 +48513,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4268" spans="1:3" hidden="1">
+    <row r="4268" spans="1:3">
       <c r="A4268" t="s">
         <v>181</v>
       </c>
@@ -48788,7 +48788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4293" spans="1:3" hidden="1">
+    <row r="4293" spans="1:3">
       <c r="A4293" t="s">
         <v>182</v>
       </c>
@@ -49063,7 +49063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4318" spans="1:3" hidden="1">
+    <row r="4318" spans="1:3">
       <c r="A4318" t="s">
         <v>183</v>
       </c>
@@ -49613,7 +49613,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4368" spans="1:3" hidden="1">
+    <row r="4368" spans="1:3">
       <c r="A4368" t="s">
         <v>186</v>
       </c>
@@ -49888,7 +49888,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4393" spans="1:3" hidden="1">
+    <row r="4393" spans="1:3">
       <c r="A4393" t="s">
         <v>187</v>
       </c>
@@ -50163,7 +50163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4418" spans="1:3" hidden="1">
+    <row r="4418" spans="1:3">
       <c r="A4418" t="s">
         <v>188</v>
       </c>
@@ -50328,7 +50328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4433" spans="1:3" hidden="1">
+    <row r="4433" spans="1:3">
       <c r="A4433" t="s">
         <v>189</v>
       </c>
@@ -50603,7 +50603,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4458" spans="1:3" hidden="1">
+    <row r="4458" spans="1:3">
       <c r="A4458" t="s">
         <v>190</v>
       </c>
@@ -50878,7 +50878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4483" spans="1:3" hidden="1">
+    <row r="4483" spans="1:3">
       <c r="A4483" t="s">
         <v>191</v>
       </c>
@@ -51153,7 +51153,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4508" spans="1:3" hidden="1">
+    <row r="4508" spans="1:3">
       <c r="A4508" t="s">
         <v>192</v>
       </c>
@@ -51428,7 +51428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4533" spans="1:3" hidden="1">
+    <row r="4533" spans="1:3">
       <c r="A4533" t="s">
         <v>193</v>
       </c>
@@ -51978,7 +51978,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4583" spans="1:3" hidden="1">
+    <row r="4583" spans="1:3">
       <c r="A4583" t="s">
         <v>195</v>
       </c>
@@ -52132,7 +52132,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4597" spans="1:3" hidden="1">
+    <row r="4597" spans="1:3">
       <c r="A4597" t="s">
         <v>196</v>
       </c>
@@ -52407,7 +52407,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4622" spans="1:3" hidden="1">
+    <row r="4622" spans="1:3">
       <c r="A4622" t="s">
         <v>197</v>
       </c>
@@ -52682,7 +52682,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4647" spans="1:3" hidden="1">
+    <row r="4647" spans="1:3">
       <c r="A4647" t="s">
         <v>198</v>
       </c>
@@ -52957,7 +52957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4672" spans="1:3" hidden="1">
+    <row r="4672" spans="1:3">
       <c r="A4672" t="s">
         <v>199</v>
       </c>
@@ -53507,7 +53507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4722" spans="1:3" hidden="1">
+    <row r="4722" spans="1:3">
       <c r="A4722" t="s">
         <v>201</v>
       </c>
@@ -53782,7 +53782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4747" spans="1:3" hidden="1">
+    <row r="4747" spans="1:3">
       <c r="A4747" t="s">
         <v>202</v>
       </c>
@@ -54057,7 +54057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4772" spans="1:3" hidden="1">
+    <row r="4772" spans="1:3">
       <c r="A4772" t="s">
         <v>203</v>
       </c>
@@ -54332,7 +54332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4797" spans="1:3" hidden="1">
+    <row r="4797" spans="1:3">
       <c r="A4797" t="s">
         <v>204</v>
       </c>
@@ -54607,7 +54607,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4822" spans="1:3" hidden="1">
+    <row r="4822" spans="1:3">
       <c r="A4822" t="s">
         <v>205</v>
       </c>
@@ -54882,7 +54882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4847" spans="1:3" hidden="1">
+    <row r="4847" spans="1:3">
       <c r="A4847" t="s">
         <v>206</v>
       </c>
@@ -55432,7 +55432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4897" spans="1:3" hidden="1">
+    <row r="4897" spans="1:3">
       <c r="A4897" t="s">
         <v>208</v>
       </c>
@@ -55982,7 +55982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4947" spans="1:3" hidden="1">
+    <row r="4947" spans="1:3">
       <c r="A4947" t="s">
         <v>210</v>
       </c>
@@ -56257,7 +56257,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4972" spans="1:3" hidden="1">
+    <row r="4972" spans="1:3">
       <c r="A4972" t="s">
         <v>211</v>
       </c>
@@ -56983,7 +56983,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5038" spans="1:3" hidden="1">
+    <row r="5038" spans="1:3">
       <c r="A5038" t="s">
         <v>214</v>
       </c>
@@ -57434,7 +57434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5079" spans="1:3" hidden="1">
+    <row r="5079" spans="1:3">
       <c r="A5079" t="s">
         <v>216</v>
       </c>
@@ -57984,7 +57984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5129" spans="1:3" hidden="1">
+    <row r="5129" spans="1:3">
       <c r="A5129" t="s">
         <v>218</v>
       </c>
@@ -58259,7 +58259,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5154" spans="1:3" hidden="1">
+    <row r="5154" spans="1:3">
       <c r="A5154" t="s">
         <v>219</v>
       </c>
@@ -58534,7 +58534,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5179" spans="1:3" hidden="1">
+    <row r="5179" spans="1:3">
       <c r="A5179" t="s">
         <v>220</v>
       </c>
@@ -58809,7 +58809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5204" spans="1:3" hidden="1">
+    <row r="5204" spans="1:3">
       <c r="A5204" t="s">
         <v>221</v>
       </c>
@@ -59084,7 +59084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5229" spans="1:3" hidden="1">
+    <row r="5229" spans="1:3">
       <c r="A5229" t="s">
         <v>222</v>
       </c>
@@ -59359,7 +59359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5254" spans="1:3" hidden="1">
+    <row r="5254" spans="1:3">
       <c r="A5254" t="s">
         <v>223</v>
       </c>
@@ -59634,7 +59634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5279" spans="1:3" hidden="1">
+    <row r="5279" spans="1:3">
       <c r="A5279" t="s">
         <v>224</v>
       </c>
@@ -60129,7 +60129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5324" spans="1:3" hidden="1">
+    <row r="5324" spans="1:3">
       <c r="A5324" t="s">
         <v>226</v>
       </c>
@@ -60404,7 +60404,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5349" spans="1:3" hidden="1">
+    <row r="5349" spans="1:3">
       <c r="A5349" t="s">
         <v>227</v>
       </c>
@@ -60679,7 +60679,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5374" spans="1:3" hidden="1">
+    <row r="5374" spans="1:3">
       <c r="A5374" t="s">
         <v>228</v>
       </c>
@@ -60954,7 +60954,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5399" spans="1:3" hidden="1">
+    <row r="5399" spans="1:3">
       <c r="A5399" t="s">
         <v>229</v>
       </c>
@@ -60970,11 +60970,6 @@
     <filterColumn colId="1">
       <filters>
         <filter val="2024"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Upper-middle-income countries"/>
       </filters>
     </filterColumn>
   </autoFilter>
